--- a/projects/r-accessible-tables/formatted_mikrozensus_sample.xlsx
+++ b/projects/r-accessible-tables/formatted_mikrozensus_sample.xlsx
@@ -7,10 +7,9 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Visual_GT_Table" sheetId="1" r:id="rId1"/>
+    <sheet name="GT_Table" sheetId="1" r:id="rId1"/>
     <sheet name="Accessible_Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Column_Structure" sheetId="3" r:id="rId3"/>
-    <sheet name="Documentation" sheetId="4" r:id="rId4"/>
+    <sheet name="Formatting_Guide" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,16 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -55,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -354,151 +342,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Col_1</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Col_2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Col_3</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Col_4</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Col_5</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>German Mikrozensus - GT-Style Formatted Table</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>German Mikrozensus - Proper GT Layout</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>[MERGE]</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>[MERGE]</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>[MERGE]</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>[MERGE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Verheiratet</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[MERGE]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[MERGE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Einkommen (%) &gt; 3000€</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Größe (cm)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Einkommen (%) &gt; 3000€</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Größe (cm)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Kategorie</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Männer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Verheiratet</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Größe (cm)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Einkommen (%) &gt; 3000€</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Größe (cm)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Kategorie</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Männer</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Frauen</t>
         </is>
@@ -511,69 +482,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Verheiratet - Einkommen (%) &gt; 3000€</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Verheiratet - Größe (cm)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Single - Einkommen (%) &gt; 3000€</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Single - Größe (cm)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Kategorie</t>
+    <row r="1">
+      <c r="A1">
+        <v>30</v>
+      </c>
+      <c r="B1">
+        <v>175</v>
+      </c>
+      <c r="C1">
+        <v>20</v>
+      </c>
+      <c r="D1">
+        <v>172</v>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Männer</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>Männer</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>165</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>168</v>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>Frauen</t>
         </is>
@@ -586,266 +530,108 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Column_Position</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Original_Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sub_Column</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Has_Spanner</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Verheiratet_Einkommen (%) &gt; 3000€</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Verheiratet</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Einkommen (%) &gt; 3000€</t>
-        </is>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Verheiratet_Größe (cm)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Verheiratet</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Größe (cm)</t>
-        </is>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Single_Einkommen (%) &gt; 3000€</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Einkommen (%) &gt; 3000€</t>
-        </is>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Single_Größe (cm)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Größe (cm)</t>
-        </is>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kategorie</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Kategorie</t>
-        </is>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Information</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Open GT_Table worksheet</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>This contains the properly structured table layout</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>German Mikrozensus - GT-Style Formatted Table</t>
+          <t>Select cells marked with [MERGE]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>These indicate cells that should be merged with the cell to their left</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>German micro census data with visual formatting that matches GT table appearance. Features visual spanner headers, professional layout, and accessibility optimization. Demonstrates proper handling of special characters (%, €, (), German umlauts).</t>
+          <t>Merge cells for title (Row 1)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Merge all cells in row 1 to create the title spanning all columns</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-11-20 13:04:28</t>
+          <t>Merge cells for spanner headers (Row 3)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Merge cells marked [MERGE] with the group name to their left</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data_Rows</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Format spanner headers</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Make spanner headers bold and centered</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data_Columns</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Structure_Type</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Grouped columns with spanners</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Number_of_Groups</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Group_Names</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Verheiratet, Single</t>
+          <t>Add borders</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Add borders around column groups and headers</t>
         </is>
       </c>
     </row>

--- a/projects/r-accessible-tables/formatted_mikrozensus_sample.xlsx
+++ b/projects/r-accessible-tables/formatted_mikrozensus_sample.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="GT_Table" sheetId="1" r:id="rId1"/>
     <sheet name="Accessible_Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Formatting_Guide" sheetId="3" r:id="rId3"/>
+    <sheet name="Table_Info" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -348,27 +348,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>German Mikrozensus - Proper GT Layout</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>[MERGE]</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>[MERGE]</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>[MERGE]</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>[MERGE]</t>
+          <t>German Mikrozensus - Clean GT Layout</t>
         </is>
       </c>
     </row>
@@ -378,19 +358,9 @@
           <t>Verheiratet</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>[MERGE]</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Single</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>[MERGE]</t>
         </is>
       </c>
     </row>
@@ -536,102 +506,102 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Open GT_Table worksheet</t>
+          <t>German Mikrozensus - Clean GT Layout</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>This contains the properly structured table layout</t>
+          <t>Row 1, spans all columns</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Structure_Type</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Select cells marked with [MERGE]</t>
+          <t>Multi-level with spanners</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>These indicate cells that should be merged with the cell to their left</t>
+          <t>Row 3: spanners, Row 4: headers</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Spanner Verheiratet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Merge cells for title (Row 1)</t>
+          <t>Spans columns 1 to 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Merge all cells in row 1 to create the title spanning all columns</t>
+          <t>Row 3, columns 1-2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Spanner Single</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Merge cells for spanner headers (Row 3)</t>
+          <t>Spans columns 3 to 4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Merge cells marked [MERGE] with the group name to their left</t>
+          <t>Row 3, columns 3-4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Data_Location</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Format spanner headers</t>
+          <t>2 data rows</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Make spanner headers bold and centered</t>
+          <t>Starting from row 6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Manual_Formatting</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Add borders</t>
+          <t>To complete GT appearance, merge empty cells with spanner headers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Add borders around column groups and headers</t>
+          <t>Use Excel merge cells function on appropriate ranges</t>
         </is>
       </c>
     </row>

--- a/projects/r-accessible-tables/formatted_mikrozensus_sample.xlsx
+++ b/projects/r-accessible-tables/formatted_mikrozensus_sample.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="GT_Table" sheetId="1" r:id="rId1"/>
     <sheet name="Accessible_Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Table_Info" sheetId="3" r:id="rId3"/>
+    <sheet name="Formatting_Instructions" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -348,7 +348,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>German Mikrozensus - Clean GT Layout</t>
+          <t>German Mikrozensus - Professional Format</t>
         </is>
       </c>
     </row>
@@ -506,102 +506,102 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>OPENXLSX_RECOMMENDED</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>German Mikrozensus - Clean GT Layout</t>
+          <t>Install openxlsx package for automatic formatting</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Row 1, spans all columns</t>
+          <t>Run: install.packages('openxlsx') then use this script</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Structure_Type</t>
+          <t>1_TITLE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Multi-level with spanners</t>
+          <t>Select A1:E1 and merge cells</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Row 3: spanners, Row 4: headers</t>
+          <t>Title should span all columns with blue background (#366092)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spanner Verheiratet</t>
+          <t>2_SPANNER_VERHEIRATET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spans columns 1 to 2</t>
+          <t>Select A3:B3 and merge cells</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Row 3, columns 1-2</t>
+          <t>Spanner Verheiratet with blue background (#4F81BD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spanner Single</t>
+          <t>2_SPANNER_SINGLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spans columns 3 to 4</t>
+          <t>Select C3:D3 and merge cells</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Row 3, columns 3-4</t>
+          <t>Spanner Single with blue background (#4F81BD)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data_Location</t>
+          <t>3_HEADERS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2 data rows</t>
+          <t>Format row 4 as headers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Starting from row 6</t>
+          <t>Light blue background (#B7D4F0), bold text, borders</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Manual_Formatting</t>
+          <t>4_DATA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>To complete GT appearance, merge empty cells with spanner headers</t>
+          <t>Format data rows (6 onwards)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Use Excel merge cells function on appropriate ranges</t>
+          <t>Light borders, center alignment, auto-fit columns</t>
         </is>
       </c>
     </row>
